--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data-Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469AE8F7-451E-4F71-9BE2-B51FBFCD83F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A901129-FAF5-4776-8E87-E69C9E87CF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Juli" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="88">
   <si>
     <t>REKAP TAHIGAN PEKERJAAN</t>
   </si>
@@ -169,6 +169,135 @@
   </si>
   <si>
     <t>Pengambilan Camera</t>
+  </si>
+  <si>
+    <t>17 Juni 2026</t>
+  </si>
+  <si>
+    <t>Toko Jangkung</t>
+  </si>
+  <si>
+    <t>Ganti HTB</t>
+  </si>
+  <si>
+    <t>30 Juni 2026</t>
+  </si>
+  <si>
+    <t>Ibu Jamilah Dispora</t>
+  </si>
+  <si>
+    <t>Pindah Pasang AC</t>
+  </si>
+  <si>
+    <t>MTsN 4 Tabalong</t>
+  </si>
+  <si>
+    <t>Perbaikan Printer Canon G3010</t>
+  </si>
+  <si>
+    <t>Linda Regency</t>
+  </si>
+  <si>
+    <t>Pink Mart</t>
+  </si>
+  <si>
+    <t>Ganti Memori Card</t>
+  </si>
+  <si>
+    <t>05 Juli 2026</t>
+  </si>
+  <si>
+    <t>H. Surian</t>
+  </si>
+  <si>
+    <t>Perbaikan CCTV dan Service AC rumah</t>
+  </si>
+  <si>
+    <t>PT. HKB</t>
+  </si>
+  <si>
+    <t>08 Juni 2026</t>
+  </si>
+  <si>
+    <t>Gudang Aset BPKAD</t>
+  </si>
+  <si>
+    <t>Fuad Seberang</t>
+  </si>
+  <si>
+    <t>Pasang Camera Ezviz Di Halte Barunak | Kelua | Muara Uya</t>
+  </si>
+  <si>
+    <t>05 Juni 2026</t>
+  </si>
+  <si>
+    <t>BSI Tanjung</t>
+  </si>
+  <si>
+    <t>Perbaikan CCTV di ATM Kemenag</t>
+  </si>
+  <si>
+    <t>Ari Oci</t>
+  </si>
+  <si>
+    <t>Perbaikan CCTV di rumah Linda 5</t>
+  </si>
+  <si>
+    <t>07 Mei 2026</t>
+  </si>
+  <si>
+    <t>Ifit (AC)</t>
+  </si>
+  <si>
+    <t>Perbaikan CCTV di MPP</t>
+  </si>
+  <si>
+    <t>06 April 2026</t>
+  </si>
+  <si>
+    <t>Pengambilan Camera H6C + Memori 128GB</t>
+  </si>
+  <si>
+    <t>Abah Nanda Loksado</t>
+  </si>
+  <si>
+    <t>Pengadaan AC</t>
+  </si>
+  <si>
+    <t>Pengambilan Monitor</t>
+  </si>
+  <si>
+    <t>Amax PolPP</t>
+  </si>
+  <si>
+    <t>Pengambilan Camera Ezviz TY1 Pro 5 Set</t>
+  </si>
+  <si>
+    <t>02 Maret 2026</t>
+  </si>
+  <si>
+    <t>19 Februari</t>
+  </si>
+  <si>
+    <t>Pengambilan Camera Imou Ranger A2</t>
+  </si>
+  <si>
+    <t>CPU Bekas + Kelengkapannya</t>
+  </si>
+  <si>
+    <t>03 Maret 2026</t>
+  </si>
+  <si>
+    <t>STM</t>
+  </si>
+  <si>
+    <t>Penambahan CCTV</t>
+  </si>
+  <si>
+    <t>RSUD H. Badaruddin Kasim</t>
+  </si>
+  <si>
+    <t>Installasi Panel Listrik</t>
   </si>
 </sst>
 </file>
@@ -176,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -259,10 +388,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -273,7 +402,7 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -282,14 +411,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -298,7 +427,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -317,27 +446,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -651,11 +759,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D327584B-2C7E-47E2-A46B-99BF2D9CC958}">
-  <dimension ref="B2:Q59"/>
+  <dimension ref="B2:Q60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="4.5703125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
     <col min="3" max="3" width="17" style="2" customWidth="1"/>
     <col min="4" max="4" width="39.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="1" customWidth="1"/>
@@ -714,16 +822,16 @@
         <v>7</v>
       </c>
       <c r="L4" s="13"/>
-      <c r="M4" s="14" t="s">
+      <c r="M4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="16">
+      <c r="B5" s="15">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -762,7 +870,7 @@
       <c r="Q5" s="7"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>2</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -799,7 +907,7 @@
       <c r="Q6" s="7"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="16">
+      <c r="B7" s="15">
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -834,7 +942,7 @@
       <c r="Q7" s="7"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="16">
+      <c r="B8" s="15">
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -863,7 +971,7 @@
       <c r="Q8" s="7"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="16">
+      <c r="B9" s="15">
         <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -886,7 +994,7 @@
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="16">
+      <c r="B10" s="15">
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -909,7 +1017,7 @@
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="16">
+      <c r="B11" s="15">
         <v>7</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -932,7 +1040,7 @@
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="16">
+      <c r="B12" s="15">
         <v>8</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -955,7 +1063,7 @@
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B13" s="16">
+      <c r="B13" s="15">
         <v>9</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -978,7 +1086,7 @@
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="16">
+      <c r="B14" s="15">
         <v>10</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -1001,260 +1109,528 @@
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="16"/>
-      <c r="C15" s="5"/>
+      <c r="B15" s="15">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="6">
+        <v>540000</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="16"/>
-      <c r="C16" s="5"/>
+      <c r="B16" s="15">
+        <v>12</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="6">
+        <v>200000</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="16"/>
-      <c r="C17" s="5"/>
+      <c r="B17" s="15">
+        <v>13</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="6">
+        <v>6501000</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="16"/>
-      <c r="C18" s="5"/>
+      <c r="B18" s="15">
+        <v>14</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D18" s="5"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="6">
+        <v>550000</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="16"/>
-      <c r="C19" s="5"/>
+      <c r="B19" s="15">
+        <v>15</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D19" s="5"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="6">
+        <v>400000</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="16"/>
-      <c r="C20" s="5"/>
+      <c r="B20" s="15">
+        <v>16</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D20" s="5"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="6">
+        <v>645000</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="16"/>
-      <c r="C21" s="5"/>
+      <c r="B21" s="15">
+        <v>17</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="6">
+        <v>235000</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="16"/>
-      <c r="C22" s="5"/>
+      <c r="B22" s="15">
+        <v>18</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="D22" s="5"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="6">
+        <v>1260000</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="16"/>
-      <c r="C23" s="5"/>
+      <c r="B23" s="15">
+        <v>19</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="6">
+        <v>312000</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="16"/>
-      <c r="C24" s="5"/>
+      <c r="B24" s="15">
+        <v>20</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="D24" s="5"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="6">
+        <v>650000</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="16"/>
-      <c r="C25" s="5"/>
+      <c r="B25" s="15">
+        <v>21</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="D25" s="5"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="6">
+        <v>3150000</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="16"/>
-      <c r="C26" s="5"/>
+      <c r="B26" s="15">
+        <v>22</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="D26" s="5"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="6">
+        <v>215000</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="16"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="15">
+        <v>23</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="D27" s="5"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="6">
+        <v>275000</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="16"/>
-      <c r="C28" s="5"/>
+      <c r="B28" s="15">
+        <v>24</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="D28" s="5"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="6">
+        <v>2605000</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="16"/>
-      <c r="C29" s="5"/>
+      <c r="B29" s="15">
+        <v>25</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="D29" s="5"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="6">
+        <v>23289000</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="16"/>
-      <c r="C30" s="5"/>
+      <c r="B30" s="15">
+        <v>26</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="D30" s="5"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G30" s="6">
+        <v>1550000</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="16"/>
-      <c r="C31" s="5"/>
+      <c r="B31" s="15">
+        <v>27</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="D31" s="5"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="6">
+        <v>24540000</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="16"/>
-      <c r="C32" s="5"/>
+      <c r="B32" s="15">
+        <v>28</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="D32" s="5"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="6">
+        <v>1277000</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="16"/>
+      <c r="B33" s="15">
+        <v>29</v>
+      </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="4"/>
+      <c r="E33" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G33" s="6">
+        <v>3250000</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="16"/>
-      <c r="C34" s="5"/>
+      <c r="B34" s="15">
+        <v>30</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="D34" s="5"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="6">
+        <v>2425000</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="16"/>
+      <c r="B35" s="15">
+        <v>31</v>
+      </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="G35" s="6"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="16"/>
-      <c r="C36" s="5"/>
+      <c r="B36" s="15">
+        <v>32</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>83</v>
+      </c>
       <c r="D36" s="5"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="6">
+        <v>728000</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="16"/>
-      <c r="C37" s="5"/>
+      <c r="B37" s="15">
+        <v>33</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="D37" s="5"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" s="6">
+        <v>21415000</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="16"/>
+      <c r="B38" s="15"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="4"/>
@@ -1265,7 +1641,7 @@
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="16"/>
+      <c r="B39" s="15"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="4"/>
@@ -1276,7 +1652,7 @@
       <c r="J39" s="4"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="16"/>
+      <c r="B40" s="15"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="4"/>
@@ -1287,7 +1663,7 @@
       <c r="J40" s="4"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="16"/>
+      <c r="B41" s="15"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="4"/>
@@ -1298,7 +1674,7 @@
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="16"/>
+      <c r="B42" s="15"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="4"/>
@@ -1309,7 +1685,7 @@
       <c r="J42" s="4"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="16"/>
+      <c r="B43" s="15"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="4"/>
@@ -1320,7 +1696,7 @@
       <c r="J43" s="4"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="16"/>
+      <c r="B44" s="15"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="4"/>
@@ -1331,7 +1707,7 @@
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="16"/>
+      <c r="B45" s="15"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="4"/>
@@ -1342,7 +1718,7 @@
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="16"/>
+      <c r="B46" s="15"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="4"/>
@@ -1353,7 +1729,7 @@
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="16"/>
+      <c r="B47" s="15"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="4"/>
@@ -1364,7 +1740,7 @@
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="16"/>
+      <c r="B48" s="15"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="4"/>
@@ -1375,7 +1751,7 @@
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="16"/>
+      <c r="B49" s="15"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="4"/>
@@ -1386,7 +1762,7 @@
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="16"/>
+      <c r="B50" s="15"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="4"/>
@@ -1397,7 +1773,7 @@
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="16"/>
+      <c r="B51" s="15"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="4"/>
@@ -1408,7 +1784,7 @@
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="16"/>
+      <c r="B52" s="15"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="4"/>
@@ -1419,7 +1795,7 @@
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="16"/>
+      <c r="B53" s="15"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="4"/>
@@ -1430,7 +1806,7 @@
       <c r="J53" s="4"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="16"/>
+      <c r="B54" s="15"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="4"/>
@@ -1441,7 +1817,7 @@
       <c r="J54" s="4"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55" s="16"/>
+      <c r="B55" s="15"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="4"/>
@@ -1452,7 +1828,7 @@
       <c r="J55" s="4"/>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="16"/>
+      <c r="B56" s="15"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="4"/>
@@ -1463,7 +1839,7 @@
       <c r="J56" s="4"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="16"/>
+      <c r="B57" s="15"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="4"/>
@@ -1474,7 +1850,7 @@
       <c r="J57" s="4"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="16"/>
+      <c r="B58" s="15"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="4"/>
@@ -1485,7 +1861,7 @@
       <c r="J58" s="4"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" s="16"/>
+      <c r="B59" s="15"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="4"/>
@@ -1495,20 +1871,26 @@
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
     </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G60" s="3">
+        <f>SUM(G5:G59)</f>
+        <v>146775000</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="M4:Q4"/>
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H59">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="DIBUAT">
-      <formula>NOT(ISERROR(SEARCH("DIBUAT",H5)))</formula>
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="DIBAYAR">
+      <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="DITAGIH">
       <formula>NOT(ISERROR(SEARCH("DITAGIH",H5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="DIBAYAR">
-      <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="DIBUAT">
+      <formula>NOT(ISERROR(SEARCH("DIBUAT",H5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">

--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data-Pekerjaan\Tagihan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A901129-FAF5-4776-8E87-E69C9E87CF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62039B61-E4EF-4473-8810-040BD8D0A28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Juli" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="110">
   <si>
     <t>REKAP TAHIGAN PEKERJAAN</t>
   </si>
@@ -298,6 +298,72 @@
   </si>
   <si>
     <t>Installasi Panel Listrik</t>
+  </si>
+  <si>
+    <t>26 Juli 2026</t>
+  </si>
+  <si>
+    <t>Pa Zulkarnain Gunung Batu</t>
+  </si>
+  <si>
+    <t>Pasang Camera Ezviz H6C 1 Paket</t>
+  </si>
+  <si>
+    <t>Pa Gani</t>
+  </si>
+  <si>
+    <t>Sudaryono</t>
+  </si>
+  <si>
+    <t>Reposisi PSU</t>
+  </si>
+  <si>
+    <t>Pa Awiek</t>
+  </si>
+  <si>
+    <t>27 Juli 2026</t>
+  </si>
+  <si>
+    <t>Ibu Guru Danau</t>
+  </si>
+  <si>
+    <t>SMA Tanta</t>
+  </si>
+  <si>
+    <t>Penarikan Kabel Fiber</t>
+  </si>
+  <si>
+    <t>Mesjid Nurul Anwar (Agung)</t>
+  </si>
+  <si>
+    <t>SDN 2 Hikun</t>
+  </si>
+  <si>
+    <t>Pa Masdar</t>
+  </si>
+  <si>
+    <t>Reposisi Camera</t>
+  </si>
+  <si>
+    <t>H. Jani</t>
+  </si>
+  <si>
+    <t>Perbaikan CCTV Tambang Jaro</t>
+  </si>
+  <si>
+    <t>SDN Lukbayur</t>
+  </si>
+  <si>
+    <t>Penambahan 2 PT Hikvision</t>
+  </si>
+  <si>
+    <t>Pengadaan Ruijie Dan Mikrotik</t>
+  </si>
+  <si>
+    <t>Imam Happy</t>
+  </si>
+  <si>
+    <t>Reposisi, Dan Setting Ulang Ezviz</t>
   </si>
 </sst>
 </file>
@@ -305,7 +371,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -388,10 +454,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -402,7 +468,7 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1284,7 +1350,7 @@
         <v>58</v>
       </c>
       <c r="G22" s="6">
-        <v>1260000</v>
+        <v>3045000</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>13</v>
@@ -1630,145 +1696,301 @@
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B38" s="15"/>
-      <c r="C38" s="5"/>
+      <c r="B38" s="15">
+        <v>34</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="D38" s="5"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G38" s="6">
+        <v>850000</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="15"/>
-      <c r="C39" s="5"/>
+      <c r="B39" s="15">
+        <v>35</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="D39" s="5"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="4"/>
+      <c r="E39" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G39" s="6">
+        <v>850000</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="15"/>
-      <c r="C40" s="5"/>
+      <c r="B40" s="15">
+        <v>36</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="D40" s="5"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="4"/>
+      <c r="E40" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G40" s="6">
+        <v>100000</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="15"/>
-      <c r="C41" s="5"/>
+      <c r="B41" s="15">
+        <v>37</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="D41" s="5"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="4"/>
+      <c r="E41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="6">
+        <v>320000</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="15"/>
-      <c r="C42" s="5"/>
+      <c r="B42" s="15">
+        <v>38</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="D42" s="5"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="4"/>
+      <c r="E42" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" s="6">
+        <v>150000</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="15"/>
-      <c r="C43" s="5"/>
+      <c r="B43" s="15">
+        <v>39</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="D43" s="5"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="4"/>
+      <c r="E43" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G43" s="6">
+        <v>400000</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="15"/>
-      <c r="C44" s="5"/>
+      <c r="B44" s="15">
+        <v>40</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="D44" s="5"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="4"/>
+      <c r="E44" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" s="6">
+        <v>1654000</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="15"/>
-      <c r="C45" s="5"/>
+      <c r="B45" s="15">
+        <v>41</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="D45" s="5"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="4"/>
+      <c r="E45" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" s="6">
+        <v>225000</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="15"/>
-      <c r="C46" s="5"/>
+      <c r="B46" s="15">
+        <v>42</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="D46" s="5"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="4"/>
+      <c r="E46" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G46" s="6">
+        <v>375000</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="15"/>
-      <c r="C47" s="5"/>
+      <c r="B47" s="15">
+        <v>42</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="D47" s="5"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="4"/>
+      <c r="E47" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G47" s="6">
+        <v>550000</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="15"/>
-      <c r="C48" s="5"/>
+      <c r="B48" s="15">
+        <v>43</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="D48" s="5"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="4"/>
+      <c r="E48" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G48" s="6">
+        <v>2605000</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="15"/>
-      <c r="C49" s="5"/>
+      <c r="B49" s="15">
+        <v>44</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="D49" s="5"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="4"/>
+      <c r="E49" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G49" s="6">
+        <v>36000000</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="15"/>
-      <c r="C50" s="5"/>
+      <c r="B50" s="15">
+        <v>45</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="D50" s="5"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="4"/>
+      <c r="E50" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G50" s="6">
+        <v>150000</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
     </row>
@@ -1874,7 +2096,7 @@
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <f>SUM(G5:G59)</f>
-        <v>146775000</v>
+        <v>192789000</v>
       </c>
     </row>
   </sheetData>

--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62039B61-E4EF-4473-8810-040BD8D0A28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A099B8B0-79DE-4D88-8498-09E444F1C61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
+    <workbookView xWindow="3510" yWindow="0" windowWidth="19410" windowHeight="15480" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Juli" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="108">
   <si>
     <t>REKAP TAHIGAN PEKERJAAN</t>
   </si>
@@ -216,12 +216,6 @@
     <t>PT. HKB</t>
   </si>
   <si>
-    <t>08 Juni 2026</t>
-  </si>
-  <si>
-    <t>Gudang Aset BPKAD</t>
-  </si>
-  <si>
     <t>Fuad Seberang</t>
   </si>
   <si>
@@ -267,12 +261,6 @@
     <t>Pengambilan Monitor</t>
   </si>
   <si>
-    <t>Amax PolPP</t>
-  </si>
-  <si>
-    <t>Pengambilan Camera Ezviz TY1 Pro 5 Set</t>
-  </si>
-  <si>
     <t>02 Maret 2026</t>
   </si>
   <si>
@@ -294,12 +282,6 @@
     <t>Penambahan CCTV</t>
   </si>
   <si>
-    <t>RSUD H. Badaruddin Kasim</t>
-  </si>
-  <si>
-    <t>Installasi Panel Listrik</t>
-  </si>
-  <si>
     <t>26 Juli 2026</t>
   </si>
   <si>
@@ -364,6 +346,18 @@
   </si>
   <si>
     <t>Reposisi, Dan Setting Ulang Ezviz</t>
+  </si>
+  <si>
+    <t>DIBAYAR</t>
+  </si>
+  <si>
+    <t>Pasang Extender HDMI</t>
+  </si>
+  <si>
+    <t>Arkha Collention</t>
+  </si>
+  <si>
+    <t>Perbaikan Komputer &amp; Perpanjang aplikasi ke toko</t>
   </si>
 </sst>
 </file>
@@ -1123,7 +1117,7 @@
         <v>3892000</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1330,7 +1324,7 @@
         <v>235000</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -1353,7 +1347,7 @@
         <v>3045000</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -1382,25 +1376,13 @@
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="15">
-        <v>20</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="B24" s="15"/>
+      <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="6">
-        <v>650000</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
@@ -1409,14 +1391,14 @@
         <v>21</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G25" s="6">
         <v>3150000</v>
@@ -1432,14 +1414,14 @@
         <v>22</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G26" s="6">
         <v>215000</v>
@@ -1459,16 +1441,16 @@
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G27" s="6">
         <v>275000</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1501,17 +1483,17 @@
         <v>25</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G29" s="6">
-        <v>23289000</v>
+        <v>8289000</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>13</v>
@@ -1524,14 +1506,14 @@
         <v>26</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G30" s="6">
         <v>1550000</v>
@@ -1547,14 +1529,14 @@
         <v>27</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G31" s="6">
         <v>24540000</v>
@@ -1570,14 +1552,14 @@
         <v>28</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G32" s="6">
         <v>1277000</v>
@@ -1589,23 +1571,13 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="15">
-        <v>29</v>
-      </c>
+      <c r="B33" s="15"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G33" s="6">
-        <v>3250000</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
     </row>
@@ -1614,14 +1586,14 @@
         <v>30</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G34" s="6">
         <v>2425000</v>
@@ -1642,7 +1614,7 @@
         <v>43</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="4"/>
@@ -1654,14 +1626,14 @@
         <v>32</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G36" s="6">
         <v>728000</v>
@@ -1673,25 +1645,13 @@
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="15">
-        <v>33</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="5"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G37" s="6">
-        <v>21415000</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
     </row>
@@ -1700,14 +1660,14 @@
         <v>34</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G38" s="6">
         <v>850000</v>
@@ -1723,14 +1683,14 @@
         <v>35</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G39" s="6">
         <v>850000</v>
@@ -1746,14 +1706,14 @@
         <v>36</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G40" s="6">
         <v>100000</v>
@@ -1769,11 +1729,11 @@
         <v>37</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>30</v>
@@ -1792,11 +1752,11 @@
         <v>38</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>30</v>
@@ -1805,7 +1765,7 @@
         <v>150000</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -1815,14 +1775,14 @@
         <v>39</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="4" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="G43" s="6">
         <v>400000</v>
@@ -1838,11 +1798,11 @@
         <v>40</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="4" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>30</v>
@@ -1851,7 +1811,7 @@
         <v>1654000</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -1861,11 +1821,11 @@
         <v>41</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>30</v>
@@ -1874,7 +1834,7 @@
         <v>225000</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -1884,20 +1844,20 @@
         <v>42</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G46" s="6">
         <v>375000</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -1907,20 +1867,20 @@
         <v>42</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="G47" s="6">
         <v>550000</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -1930,20 +1890,20 @@
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G48" s="6">
         <v>2605000</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -1953,14 +1913,14 @@
         <v>44</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G49" s="6">
         <v>36000000</v>
@@ -1976,14 +1936,14 @@
         <v>45</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G50" s="6">
         <v>150000</v>
@@ -1995,24 +1955,48 @@
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="15"/>
-      <c r="C51" s="5"/>
+      <c r="B51" s="15">
+        <v>46</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="D51" s="5"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="4"/>
+      <c r="E51" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G51" s="6">
+        <v>10600000</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="15"/>
-      <c r="C52" s="5"/>
+      <c r="B52" s="15">
+        <v>47</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="D52" s="5"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="4"/>
+      <c r="E52" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G52" s="6">
+        <v>800000</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
     </row>
@@ -2096,7 +2080,7 @@
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <f>SUM(G5:G59)</f>
-        <v>192789000</v>
+        <v>163874000</v>
       </c>
     </row>
   </sheetData>

--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A099B8B0-79DE-4D88-8498-09E444F1C61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE697C05-F17C-4A36-9B88-CFDD74F99FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="0" windowWidth="19410" windowHeight="15480" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Juli" sheetId="1" r:id="rId1"/>
+    <sheet name="Agustus" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="117">
   <si>
     <t>REKAP TAHIGAN PEKERJAAN</t>
   </si>
@@ -358,6 +359,33 @@
   </si>
   <si>
     <t>Perbaikan Komputer &amp; Perpanjang aplikasi ke toko</t>
+  </si>
+  <si>
+    <t>30 Juli 2026</t>
+  </si>
+  <si>
+    <t>Doni AC</t>
+  </si>
+  <si>
+    <t>Pengambilan Camera Proview</t>
+  </si>
+  <si>
+    <t>04 Agustus 2026</t>
+  </si>
+  <si>
+    <t>Nfour Mart</t>
+  </si>
+  <si>
+    <t>Pemasangan CCTV dan Komputer Kasir</t>
+  </si>
+  <si>
+    <t>TK Muhammadiyah</t>
+  </si>
+  <si>
+    <t>Pergantian Memori Card 32GB</t>
+  </si>
+  <si>
+    <t>Kantor Desa Mangkusip</t>
   </si>
 </sst>
 </file>
@@ -487,7 +515,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2001,13 +2050,25 @@
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="15"/>
-      <c r="C53" s="5"/>
+      <c r="B53" s="15">
+        <v>48</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="D53" s="5"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="4"/>
+      <c r="E53" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G53" s="6">
+        <v>1260000</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
@@ -2080,13 +2141,797 @@
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G60" s="3">
         <f>SUM(G5:G59)</f>
-        <v>163874000</v>
+        <v>165134000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="M4:Q4"/>
     <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H5:H59">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="DIBAYAR">
+      <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="DITAGIH">
+      <formula>NOT(ISERROR(SEARCH("DITAGIH",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="DIBUAT">
+      <formula>NOT(ISERROR(SEARCH("DIBUAT",H5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H59" xr:uid="{997EDEF8-F9DB-4A95-AD74-5BE3FAC1D8B0}">
+      <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I59" xr:uid="{6425F9F2-78D3-4239-A45C-E9E345771C7D}">
+      <formula1>"TUNAI,TRANSFER"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867879EA-6F57-4527-BD9D-B58F88ECFB1A}">
+  <dimension ref="B2:Q60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="17" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="74.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" style="3" customWidth="1"/>
+    <col min="8" max="9" width="22" style="1" customWidth="1"/>
+    <col min="10" max="10" width="51.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="3.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="1.42578125" style="1" customWidth="1"/>
+    <col min="15" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="3.5703125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+    </row>
+    <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="15">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="6">
+        <v>39194000</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="15">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="6">
+        <v>230000</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="15"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="6">
+        <v>155000</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B8" s="15"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="15"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B11" s="15"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B14" s="15"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="15"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="15"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="15"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="15"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="15"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="15"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="15"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="15"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="15"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="15"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="15"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="15"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="15"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="15"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="15"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="15"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="15"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="15"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="15"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="15"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="15"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="15"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="15"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="15"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="15"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="15"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="15"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="15"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="15"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="15"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="15"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="15"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="15"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="15"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="15"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="15"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="15"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="15"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="15"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="15"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="15"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="15"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G60" s="3">
+        <f>SUM(G5:G59)</f>
+        <v>39579000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="M4:Q4"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H59">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="DIBAYAR">
@@ -2100,11 +2945,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H59" xr:uid="{997EDEF8-F9DB-4A95-AD74-5BE3FAC1D8B0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I59" xr:uid="{8D463466-EF54-4372-8845-E37C7920DA1D}">
+      <formula1>"TUNAI,TRANSFER"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H59" xr:uid="{1B647AD2-72F7-4B88-B373-83AD8FAE4C47}">
       <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I59" xr:uid="{6425F9F2-78D3-4239-A45C-E9E345771C7D}">
-      <formula1>"TUNAI,TRANSFER"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE697C05-F17C-4A36-9B88-CFDD74F99FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60ECD5C-EE9D-4632-A2B1-9A4A920BDA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" activeTab="1" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Juli" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="145">
   <si>
     <t>REKAP TAHIGAN PEKERJAAN</t>
   </si>
@@ -199,9 +199,6 @@
     <t>Linda Regency</t>
   </si>
   <si>
-    <t>Pink Mart</t>
-  </si>
-  <si>
     <t>Ganti Memori Card</t>
   </si>
   <si>
@@ -386,6 +383,93 @@
   </si>
   <si>
     <t>Kantor Desa Mangkusip</t>
+  </si>
+  <si>
+    <t>05 Agustus 2026</t>
+  </si>
+  <si>
+    <t>Isar</t>
+  </si>
+  <si>
+    <t>Ezviz H8C</t>
+  </si>
+  <si>
+    <t>Koni Tabalong</t>
+  </si>
+  <si>
+    <t>Service AC</t>
+  </si>
+  <si>
+    <t>Bawaslu</t>
+  </si>
+  <si>
+    <t>Installasi CCTV</t>
+  </si>
+  <si>
+    <t>Ezviz H6C</t>
+  </si>
+  <si>
+    <t>Janu Aresha</t>
+  </si>
+  <si>
+    <t>Paket Ezviz H6C</t>
+  </si>
+  <si>
+    <t>Sudarsono</t>
+  </si>
+  <si>
+    <t>Dillah TKJ</t>
+  </si>
+  <si>
+    <t>Pemasangan CCTV Dishub Dan SD Muhammadiyah</t>
+  </si>
+  <si>
+    <t>Dinas Sosial</t>
+  </si>
+  <si>
+    <t>Perbaikan Laptop Printer Dan UPS</t>
+  </si>
+  <si>
+    <t>Inspektorat</t>
+  </si>
+  <si>
+    <t>Pemasangan AP Ruijie</t>
+  </si>
+  <si>
+    <t>Gudang Aset Pendopo</t>
+  </si>
+  <si>
+    <t>Karaoke Marmus</t>
+  </si>
+  <si>
+    <t>Riska (Permata baru)</t>
+  </si>
+  <si>
+    <t>Pasang dan Setting CCTV</t>
+  </si>
+  <si>
+    <t>Denso</t>
+  </si>
+  <si>
+    <t>H. Adil</t>
+  </si>
+  <si>
+    <t>Perbaikan Listrik</t>
+  </si>
+  <si>
+    <t>MBG Plamboyan</t>
+  </si>
+  <si>
+    <t>SDN Pembataan 1</t>
+  </si>
+  <si>
+    <t>Bos Oyong Keloa</t>
+  </si>
+  <si>
+    <t>Pasang CCTV 2 Camera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
   </si>
 </sst>
 </file>
@@ -472,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -505,6 +589,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -890,17 +975,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
     </row>
     <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -931,13 +1016,13 @@
         <v>7</v>
       </c>
       <c r="L4" s="13"/>
-      <c r="M4" s="16" t="s">
+      <c r="M4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="15">
@@ -1166,7 +1251,7 @@
         <v>3892000</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1364,10 +1449,10 @@
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="G21" s="6">
         <v>235000</v>
@@ -1383,14 +1468,14 @@
         <v>18</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="G22" s="6">
         <v>3045000</v>
@@ -1410,7 +1495,7 @@
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>30</v>
@@ -1440,14 +1525,14 @@
         <v>21</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="G25" s="6">
         <v>3150000</v>
@@ -1463,14 +1548,14 @@
         <v>22</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="G26" s="6">
         <v>215000</v>
@@ -1490,16 +1575,16 @@
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="G27" s="6">
         <v>275000</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1513,7 +1598,7 @@
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>30</v>
@@ -1532,14 +1617,14 @@
         <v>25</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="G29" s="6">
         <v>8289000</v>
@@ -1555,14 +1640,14 @@
         <v>26</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G30" s="6">
         <v>1550000</v>
@@ -1578,14 +1663,14 @@
         <v>27</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="G31" s="6">
         <v>24540000</v>
@@ -1601,14 +1686,14 @@
         <v>28</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G32" s="6">
         <v>1277000</v>
@@ -1635,14 +1720,14 @@
         <v>30</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="4" t="s">
         <v>43</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G34" s="6">
         <v>2425000</v>
@@ -1663,7 +1748,7 @@
         <v>43</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="4"/>
@@ -1675,14 +1760,14 @@
         <v>32</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>81</v>
       </c>
       <c r="G36" s="6">
         <v>728000</v>
@@ -1709,14 +1794,14 @@
         <v>34</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="G38" s="6">
         <v>850000</v>
@@ -1732,14 +1817,14 @@
         <v>35</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G39" s="6">
         <v>850000</v>
@@ -1755,14 +1840,14 @@
         <v>36</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="G40" s="6">
         <v>100000</v>
@@ -1778,11 +1863,11 @@
         <v>37</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>30</v>
@@ -1801,11 +1886,11 @@
         <v>38</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>30</v>
@@ -1814,7 +1899,7 @@
         <v>150000</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -1824,14 +1909,14 @@
         <v>39</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="G43" s="6">
         <v>400000</v>
@@ -1847,11 +1932,11 @@
         <v>40</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>30</v>
@@ -1870,11 +1955,11 @@
         <v>41</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>30</v>
@@ -1893,20 +1978,20 @@
         <v>42</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="G46" s="6">
         <v>375000</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -1916,14 +2001,14 @@
         <v>42</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="G47" s="6">
         <v>550000</v>
@@ -1939,14 +2024,14 @@
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="G48" s="6">
         <v>2605000</v>
@@ -1962,14 +2047,14 @@
         <v>44</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G49" s="6">
         <v>36000000</v>
@@ -1985,14 +2070,14 @@
         <v>45</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="G50" s="6">
         <v>150000</v>
@@ -2008,14 +2093,14 @@
         <v>46</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="4" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G51" s="6">
         <v>10600000</v>
@@ -2031,14 +2116,14 @@
         <v>47</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="G52" s="6">
         <v>800000</v>
@@ -2054,14 +2139,14 @@
         <v>48</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="G53" s="6">
         <v>1260000</v>
@@ -2139,7 +2224,7 @@
       <c r="J59" s="4"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G60" s="3">
+      <c r="G60" s="16">
         <f>SUM(G5:G59)</f>
         <v>165134000</v>
       </c>
@@ -2174,7 +2259,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867879EA-6F57-4527-BD9D-B58F88ECFB1A}">
-  <dimension ref="B2:Q60"/>
+  <dimension ref="B2:Q61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2196,17 +2281,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
     </row>
     <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -2237,27 +2322,27 @@
         <v>7</v>
       </c>
       <c r="L4" s="13"/>
-      <c r="M4" s="16" t="s">
+      <c r="M4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="15">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="G5" s="6">
         <v>39194000</v>
@@ -2281,16 +2366,14 @@
       <c r="Q5" s="7"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="15">
-        <v>2</v>
-      </c>
+      <c r="B6" s="15"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="G6" s="6">
         <v>230000</v>
@@ -2318,7 +2401,7 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>30</v>
@@ -2348,10 +2431,18 @@
       <c r="B8" s="15"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1200000</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="L8" s="7"/>
@@ -2362,24 +2453,50 @@
       <c r="Q8" s="7"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="15"/>
-      <c r="C9" s="5"/>
+      <c r="B9" s="15">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="6">
+        <v>940000</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="15"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G10" s="6">
+        <v>700000</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
@@ -2387,10 +2504,18 @@
       <c r="B11" s="15"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" s="6">
+        <v>665000</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
@@ -2398,10 +2523,18 @@
       <c r="B12" s="15"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="6">
+        <v>850000</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
@@ -2409,10 +2542,18 @@
       <c r="B13" s="15"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1600000</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
@@ -2420,10 +2561,18 @@
       <c r="B14" s="15"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="6">
+        <v>17104000</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
     </row>
@@ -2431,10 +2580,18 @@
       <c r="B15" s="15"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G15" s="6">
+        <v>1250000</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
     </row>
@@ -2442,10 +2599,18 @@
       <c r="B16" s="15"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G16" s="6">
+        <v>1135000</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
     </row>
@@ -2453,10 +2618,18 @@
       <c r="B17" s="15"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="4"/>
+      <c r="E17" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="6">
+        <v>300000</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
     </row>
@@ -2464,10 +2637,18 @@
       <c r="B18" s="15"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1700000</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
     </row>
@@ -2475,10 +2656,18 @@
       <c r="B19" s="15"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G19" s="6">
+        <v>180000</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
@@ -2486,10 +2675,18 @@
       <c r="B20" s="15"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="6">
+        <v>185000</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
@@ -2497,10 +2694,18 @@
       <c r="B21" s="15"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G21" s="6">
+        <v>155000</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
@@ -2508,10 +2713,18 @@
       <c r="B22" s="15"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="6">
+        <v>938000</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
     </row>
@@ -2519,10 +2732,18 @@
       <c r="B23" s="15"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="6">
+        <v>180000</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
     </row>
@@ -2530,10 +2751,18 @@
       <c r="B24" s="15"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G24" s="6">
+        <v>3200000</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
@@ -2923,9 +3152,20 @@
       <c r="J59" s="4"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G60" s="3">
-        <f>SUM(G5:G59)</f>
-        <v>39579000</v>
+      <c r="B60" s="15"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G61" s="16">
+        <f>SUM(G5:G60)</f>
+        <v>71861000</v>
       </c>
     </row>
   </sheetData>
@@ -2933,7 +3173,7 @@
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H59">
+  <conditionalFormatting sqref="H5:H60">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
@@ -2945,10 +3185,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I59" xr:uid="{8D463466-EF54-4372-8845-E37C7920DA1D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I60" xr:uid="{8D463466-EF54-4372-8845-E37C7920DA1D}">
       <formula1>"TUNAI,TRANSFER"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H59" xr:uid="{1B647AD2-72F7-4B88-B373-83AD8FAE4C47}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H60" xr:uid="{1B647AD2-72F7-4B88-B373-83AD8FAE4C47}">
       <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60ECD5C-EE9D-4632-A2B1-9A4A920BDA1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD52516A-4DD5-46A9-835F-52AE62BC8803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Juli" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="169">
   <si>
     <t>REKAP TAHIGAN PEKERJAAN</t>
   </si>
@@ -470,6 +470,78 @@
   </si>
   <si>
     <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>Zosef Taufan</t>
+  </si>
+  <si>
+    <t>Paket 4 Kamera Hilook Standart</t>
+  </si>
+  <si>
+    <t>Happy mart</t>
+  </si>
+  <si>
+    <t>TK Al Umm</t>
+  </si>
+  <si>
+    <t>Pemasangan Kamera Ezviz dan AP Foredge</t>
+  </si>
+  <si>
+    <t>Service AC dan Service Printer</t>
+  </si>
+  <si>
+    <t>Pamarangan</t>
+  </si>
+  <si>
+    <t>Pemasangan CCTV</t>
+  </si>
+  <si>
+    <t>Hj Ami</t>
+  </si>
+  <si>
+    <t>Dealer Yamaha Mabuun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H Surian </t>
+  </si>
+  <si>
+    <t>H Uri</t>
+  </si>
+  <si>
+    <t>Devi Kosmetik</t>
+  </si>
+  <si>
+    <t>Pindah Pasang Ezviz</t>
+  </si>
+  <si>
+    <t>Kambitin Raya</t>
+  </si>
+  <si>
+    <t>Setting Ulang Ezviz</t>
+  </si>
+  <si>
+    <t>Hanafi</t>
+  </si>
+  <si>
+    <t>Rufi</t>
+  </si>
+  <si>
+    <t>H Adil</t>
+  </si>
+  <si>
+    <t>Pergantian PSU 8ch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pa Awiek </t>
+  </si>
+  <si>
+    <t>Perbaikan CCTV dan Harddisk External baru</t>
+  </si>
+  <si>
+    <t>G.H. Safira</t>
+  </si>
+  <si>
+    <t>NSS</t>
   </si>
 </sst>
 </file>
@@ -477,7 +549,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -560,10 +632,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -574,7 +646,7 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -589,7 +661,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -657,9 +729,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -697,7 +769,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -803,7 +875,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -945,7 +1017,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2259,7 +2331,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867879EA-6F57-4527-BD9D-B58F88ECFB1A}">
-  <dimension ref="B2:Q61"/>
+  <dimension ref="B2:Q60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2770,10 +2842,18 @@
       <c r="B25" s="15"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G25" s="6">
+        <v>2625000</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
     </row>
@@ -2781,10 +2861,18 @@
       <c r="B26" s="15"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G26" s="6">
+        <v>300000</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
@@ -2792,10 +2880,18 @@
       <c r="B27" s="15"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="6">
+        <v>4630000</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
     </row>
@@ -2803,10 +2899,18 @@
       <c r="B28" s="15"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G28" s="6">
+        <v>756000</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
     </row>
@@ -2814,10 +2918,18 @@
       <c r="B29" s="15"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G29" s="6">
+        <v>1600000</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
     </row>
@@ -2825,10 +2937,18 @@
       <c r="B30" s="15"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="6">
+        <v>382000</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
     </row>
@@ -2836,10 +2956,18 @@
       <c r="B31" s="15"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="6">
+        <v>490000</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
     </row>
@@ -2847,10 +2975,18 @@
       <c r="B32" s="15"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" s="6">
+        <v>350000</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
     </row>
@@ -2858,10 +2994,18 @@
       <c r="B33" s="15"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="4"/>
+      <c r="E33" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" s="6">
+        <v>440000</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
     </row>
@@ -2869,10 +3013,18 @@
       <c r="B34" s="15"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G34" s="6">
+        <v>75000</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
@@ -2880,10 +3032,18 @@
       <c r="B35" s="15"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G35" s="6">
+        <v>300000</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
@@ -2891,10 +3051,18 @@
       <c r="B36" s="15"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" s="6">
+        <v>150000</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
@@ -2902,10 +3070,18 @@
       <c r="B37" s="15"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G37" s="6">
+        <v>250000</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
     </row>
@@ -2913,10 +3089,18 @@
       <c r="B38" s="15"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G38" s="6">
+        <v>415000</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
@@ -2924,10 +3108,18 @@
       <c r="B39" s="15"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="4"/>
+      <c r="E39" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G39" s="6">
+        <v>300000</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
     </row>
@@ -2935,10 +3127,18 @@
       <c r="B40" s="15"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="4"/>
+      <c r="E40" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G40" s="6">
+        <v>200000</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
     </row>
@@ -3152,20 +3352,9 @@
       <c r="J59" s="4"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="15"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G61" s="16">
-        <f>SUM(G5:G60)</f>
-        <v>71861000</v>
+      <c r="G60" s="16">
+        <f>SUM(G5:G59)</f>
+        <v>85124000</v>
       </c>
     </row>
   </sheetData>
@@ -3173,7 +3362,7 @@
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H60">
+  <conditionalFormatting sqref="H5:H59">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
@@ -3185,10 +3374,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I60" xr:uid="{8D463466-EF54-4372-8845-E37C7920DA1D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I59" xr:uid="{8D463466-EF54-4372-8845-E37C7920DA1D}">
       <formula1>"TUNAI,TRANSFER"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H60" xr:uid="{1B647AD2-72F7-4B88-B373-83AD8FAE4C47}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H59" xr:uid="{1B647AD2-72F7-4B88-B373-83AD8FAE4C47}">
       <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
     </dataValidation>
   </dataValidations>
